--- a/deliverables/qc_register/QC_Batch_Release_Results_Register.xlsx
+++ b/deliverables/qc_register/QC_Batch_Release_Results_Register.xlsx
@@ -642,7 +642,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per certificate · "/" = not tested on that certificate · grouped per batch · source: RAGFlow eCoA_DATABASE (291 certificates, sanity-checked) · grades: ImB_Potency_Grade_Ranges (mandatory management codes, symmetric balanced tolerances)</t>
+          <t>One row per certificate · "/" = not tested on that certificate · grouped per batch · source: RAGFlow eCoA_DATABASE (291 certificates, sanity-checked) · grades: ImB_Potency_Grade_Ranges (mandatory management codes revised 27.08.2026, symmetric balanced tolerances, anchors = T1+T2 re-analysis of 26.08.2026 where retested — T2 values unofficial pending formal eCoAs)</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AE18" s="8" t="inlineStr">
         <is>
-          <t>I · CJ_THC24 : CBD1</t>
+          <t>III · CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF18" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-I</t>
+          <t>QCSP_001_CJ-III</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="AE28" s="8" t="inlineStr">
         <is>
-          <t>II · GP_THC20 : CBD1</t>
+          <t>IV · GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF28" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="AE33" s="8" t="inlineStr">
         <is>
-          <t>III · GG_THC14 : CBD1</t>
+          <t>II · GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="AF33" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-III</t>
+          <t>QCSP_001_GG-II</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>17.00 – 19.00 %</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="AE34" s="8" t="inlineStr">
         <is>
-          <t>II · HPA_THC18 : CBD1</t>
+          <t>III · HPA_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AF34" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-II</t>
+          <t>QCSP_001_HPA-III</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>19.80 – 24.20 %</t>
+          <t>19.81 – 24.19 %</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>17.01 – 18.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="AE44" s="8" t="inlineStr">
         <is>
-          <t>III · OPM_THC16 : CBD1</t>
+          <t>II · OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AF44" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="AE52" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>III · GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF52" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>21.00 – 23.00 %</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>26.61 – 29.39 %</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AE81" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>I · GP_THC28 : CBD1</t>
         </is>
       </c>
       <c r="AF81" s="7" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>15.00 – 17.00 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
@@ -12607,12 +12607,12 @@
       </c>
       <c r="AE88" s="8" t="inlineStr">
         <is>
-          <t>II · MB_THC16 : CBD1</t>
+          <t>I · MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AF88" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-II</t>
+          <t>QCSP_001_MB-I</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
@@ -13175,12 +13175,12 @@
       </c>
       <c r="AE92" s="8" t="inlineStr">
         <is>
-          <t>III · OPM_THC16 : CBD1</t>
+          <t>II · OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AF92" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="AE96" s="8" t="inlineStr">
         <is>
-          <t>IV · OPM_THC14 : CBD1</t>
+          <t>III · OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="AF96" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="AE100" s="8" t="inlineStr">
         <is>
-          <t>I · CJ_THC24 : CBD1</t>
+          <t>III · CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF100" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-I</t>
+          <t>QCSP_001_CJ-III</t>
         </is>
       </c>
     </row>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="AE106" s="8" t="inlineStr">
         <is>
-          <t>III · CJ_THC16 : CBD1</t>
+          <t>V · CJ_THC16 : CBD1</t>
         </is>
       </c>
       <c r="AF106" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-III</t>
+          <t>QCSP_001_CJ-V</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>17.37 – 18.63 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
@@ -15719,12 +15719,12 @@
       </c>
       <c r="AE110" s="8" t="inlineStr">
         <is>
-          <t>III · GP_THC18 : CBD1</t>
+          <t>IV · GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF110" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-III</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>19.01 – 20.99 %</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="AE115" s="8" t="inlineStr">
         <is>
-          <t>I · HPA_THC22 : CBD1</t>
+          <t>II · HPA_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF115" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-I</t>
+          <t>QCSP_001_HPA-II</t>
         </is>
       </c>
     </row>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
@@ -16991,12 +16991,12 @@
       </c>
       <c r="AE119" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>III · GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF119" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
     </row>
@@ -18239,12 +18239,12 @@
       </c>
       <c r="AE128" s="8" t="inlineStr">
         <is>
-          <t>II · CJ_THC20 : CBD1</t>
+          <t>IV · CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF128" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-II</t>
+          <t>QCSP_001_CJ-IV</t>
         </is>
       </c>
     </row>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>18.00 – 22.00 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
@@ -19079,12 +19079,12 @@
       </c>
       <c r="AE134" s="8" t="inlineStr">
         <is>
-          <t>II · CJ_THC20 : CBD1</t>
+          <t>III · CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF134" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-II</t>
+          <t>QCSP_001_CJ-III</t>
         </is>
       </c>
     </row>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
@@ -20487,12 +20487,12 @@
       </c>
       <c r="AE144" s="8" t="inlineStr">
         <is>
-          <t>I · CJ_THC24 : CBD1</t>
+          <t>III · CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF144" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-I</t>
+          <t>QCSP_001_CJ-III</t>
         </is>
       </c>
     </row>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AE151" s="8" t="inlineStr">
         <is>
-          <t>III · PM_THC10 : CBD1</t>
+          <t>II · PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="AF151" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
     </row>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
@@ -22487,12 +22487,12 @@
       </c>
       <c r="AE158" s="8" t="inlineStr">
         <is>
-          <t>II · GP_THC20 : CBD1</t>
+          <t>IV · GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF158" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
     </row>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -23055,12 +23055,12 @@
       </c>
       <c r="AE162" s="8" t="inlineStr">
         <is>
-          <t>II · GP_THC20 : CBD1</t>
+          <t>IV · GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF162" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
     </row>
@@ -23498,7 +23498,7 @@
       </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
@@ -23623,12 +23623,12 @@
       </c>
       <c r="AE166" s="8" t="inlineStr">
         <is>
-          <t>II · GP_THC20 : CBD1</t>
+          <t>III · GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF166" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
     </row>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>14.64 – 17.36 %</t>
+          <t>14.40 – 17.60 %</t>
         </is>
       </c>
       <c r="G170" s="9" t="inlineStr">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="AE170" s="8" t="inlineStr">
         <is>
-          <t>IV · GP_THC16 : CBD1</t>
+          <t>V · GP_THC16 : CBD1</t>
         </is>
       </c>
       <c r="AF170" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-IV</t>
+          <t>QCSP_001_GP-V</t>
         </is>
       </c>
     </row>
@@ -25599,12 +25599,12 @@
       </c>
       <c r="AE180" s="8" t="inlineStr">
         <is>
-          <t>II · CJ_THC20 : CBD1</t>
+          <t>IV · CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF180" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-II</t>
+          <t>QCSP_001_CJ-IV</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="F186" s="10" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>27.00 – 29.00 %</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="AE186" s="8" t="inlineStr">
         <is>
-          <t>I · CJ_THC24 : CBD1</t>
+          <t>I · CJ_THC28 : CBD1</t>
         </is>
       </c>
       <c r="AF186" s="7" t="inlineStr">
@@ -26882,7 +26882,7 @@
       </c>
       <c r="F190" s="10" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>25.01 – 26.99 %</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
@@ -27007,12 +27007,12 @@
       </c>
       <c r="AE190" s="8" t="inlineStr">
         <is>
-          <t>I · CJ_THC24 : CBD1</t>
+          <t>II · CJ_THC26 : CBD1</t>
         </is>
       </c>
       <c r="AF190" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-I</t>
+          <t>QCSP_001_CJ-II</t>
         </is>
       </c>
     </row>
@@ -27450,7 +27450,7 @@
       </c>
       <c r="F194" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
@@ -27575,12 +27575,12 @@
       </c>
       <c r="AE194" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>III · GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF194" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
     </row>
@@ -28143,12 +28143,12 @@
       </c>
       <c r="AE198" s="8" t="inlineStr">
         <is>
-          <t>V · OPM_THC10 : CBD1</t>
+          <t>IV · OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="AF198" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
     </row>
@@ -28711,12 +28711,12 @@
       </c>
       <c r="AE202" s="8" t="inlineStr">
         <is>
-          <t>II · PM_THC12 : CBD1</t>
+          <t>I · PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="AF202" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-II</t>
+          <t>QCSP_001_PM-I</t>
         </is>
       </c>
     </row>
@@ -30562,7 +30562,7 @@
       </c>
       <c r="F216" s="10" t="inlineStr">
         <is>
-          <t>10.80 – 13.20 %</t>
+          <t>9.00 – 11.00 %</t>
         </is>
       </c>
       <c r="G216" s="9" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="AE216" s="8" t="inlineStr">
         <is>
-          <t>I · GRC_THC12 : CBD1</t>
+          <t>I · GRC_THC10 : CBD1</t>
         </is>
       </c>
       <c r="AF216" s="7" t="inlineStr">
@@ -33275,12 +33275,12 @@
       </c>
       <c r="AE234" s="8" t="inlineStr">
         <is>
-          <t>VI · OPM_THC8 : CBD1</t>
+          <t>V · OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="AF234" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33310,7 @@
       </c>
       <c r="F235" s="10" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>9.00 – 11.00 %</t>
         </is>
       </c>
       <c r="G235" s="9" t="inlineStr">
@@ -33435,12 +33435,12 @@
       </c>
       <c r="AE235" s="8" t="inlineStr">
         <is>
-          <t>I · PM_THC14 : CBD1</t>
+          <t>II · PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="AF235" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-I</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
     </row>
@@ -34459,12 +34459,12 @@
       </c>
       <c r="AE242" s="8" t="inlineStr">
         <is>
-          <t>VI · OPM_THC8 : CBD1</t>
+          <t>V · OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="AF242" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F248" s="10" t="inlineStr">
         <is>
-          <t>13.01 – 14.99 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="G248" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
       </c>
       <c r="F251" s="10" t="inlineStr">
         <is>
-          <t>13.01 – 14.99 %</t>
+          <t>17.15 – 18.85 %</t>
         </is>
       </c>
       <c r="G251" s="9" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="AE251" s="8" t="inlineStr">
         <is>
-          <t>III · FB_THC14 : CBD1</t>
+          <t>II · FB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AF251" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-III</t>
+          <t>QCSP_001_FB-II</t>
         </is>
       </c>
     </row>
@@ -36038,7 +36038,7 @@
       </c>
       <c r="F254" s="10" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>14.86 – 17.14 %</t>
         </is>
       </c>
       <c r="G254" s="9" t="inlineStr">
@@ -36163,12 +36163,12 @@
       </c>
       <c r="AE254" s="8" t="inlineStr">
         <is>
-          <t>II · FB_THC18 : CBD1</t>
+          <t>III · FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="AF254" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-II</t>
+          <t>QCSP_001_FB-III</t>
         </is>
       </c>
     </row>
@@ -36470,7 +36470,7 @@
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="G257" s="9" t="inlineStr">
@@ -36902,7 +36902,7 @@
       </c>
       <c r="F260" s="10" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="G260" s="9" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="F271" s="10" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>13.10 – 14.90 %</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
@@ -39326,7 +39326,7 @@
       </c>
       <c r="F277" s="10" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>18.86 – 21.14 %</t>
         </is>
       </c>
       <c r="G277" s="9" t="inlineStr">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="AE277" s="8" t="inlineStr">
         <is>
-          <t>I · FB_THC22 : CBD1</t>
+          <t>I · FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF277" s="7" t="inlineStr">
@@ -39486,7 +39486,7 @@
       </c>
       <c r="F278" s="10" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>17.15 – 18.85 %</t>
         </is>
       </c>
       <c r="G278" s="9" t="inlineStr">
@@ -39646,7 +39646,7 @@
       </c>
       <c r="F279" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="G279" s="9" t="inlineStr">
@@ -40078,7 +40078,7 @@
       </c>
       <c r="F282" s="10" t="inlineStr">
         <is>
-          <t>18.00 – 22.00 %</t>
+          <t>13.10 – 14.90 %</t>
         </is>
       </c>
       <c r="G282" s="9" t="inlineStr">
@@ -40203,12 +40203,12 @@
       </c>
       <c r="AE282" s="8" t="inlineStr">
         <is>
-          <t>I · JD_THC20 : CBD1</t>
+          <t>III · JD_THC14 : CBD1</t>
         </is>
       </c>
       <c r="AF282" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-I</t>
+          <t>QCSP_001_JD-III</t>
         </is>
       </c>
     </row>
@@ -40238,7 +40238,7 @@
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>14.91 – 17.09 %</t>
         </is>
       </c>
       <c r="G283" s="9" t="inlineStr">
@@ -40554,7 +40554,7 @@
       </c>
       <c r="F285" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>25.40 – 26.60 %</t>
         </is>
       </c>
       <c r="G285" s="9" t="inlineStr">
@@ -40679,12 +40679,12 @@
       </c>
       <c r="AE285" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>II · GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="AF285" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-II</t>
         </is>
       </c>
     </row>
@@ -40714,7 +40714,7 @@
       </c>
       <c r="F286" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>25.40 – 26.60 %</t>
         </is>
       </c>
       <c r="G286" s="9" t="inlineStr">
@@ -40839,12 +40839,12 @@
       </c>
       <c r="AE286" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>II · GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="AF286" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-II</t>
         </is>
       </c>
     </row>
@@ -40874,7 +40874,7 @@
       </c>
       <c r="F287" s="10" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="G287" s="9" t="inlineStr">
@@ -40999,12 +40999,12 @@
       </c>
       <c r="AE287" s="8" t="inlineStr">
         <is>
-          <t>I · GP_THC24 : CBD1</t>
+          <t>III · GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AF287" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
     </row>
@@ -41186,7 +41186,7 @@
       </c>
       <c r="F289" s="10" t="inlineStr">
         <is>
-          <t>11.00 – 13.00 %</t>
+          <t>10.80 – 13.20 %</t>
         </is>
       </c>
       <c r="G289" s="9" t="inlineStr">
@@ -41342,7 +41342,7 @@
       </c>
       <c r="F290" s="10" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="G290" s="9" t="inlineStr">
@@ -41798,7 +41798,7 @@
       </c>
       <c r="F293" s="10" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>18.86 – 21.14 %</t>
         </is>
       </c>
       <c r="G293" s="9" t="inlineStr">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="AE293" s="8" t="inlineStr">
         <is>
-          <t>II · FB_THC18 : CBD1</t>
+          <t>I · FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF293" s="7" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-II</t>
+          <t>QCSP_001_FB-I</t>
         </is>
       </c>
     </row>
@@ -42368,7 +42368,7 @@
       <c r="A298" s="9" t="inlineStr"/>
       <c r="B298" s="16" t="inlineStr">
         <is>
-          <t>PENDING — no eCoA on file (grades provisional, declared values)</t>
+          <t>PENDING — no eCoA on file (grades provisional: owner-declared values, or unofficial T2 re-analysis values of 26.08.2026)</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42388,7 @@
       </c>
       <c r="E299" s="20" t="inlineStr">
         <is>
-          <t>12.91 (declared)</t>
+          <t>12.09 (Т2 26.08.2026 (неофиц. | unofficial))</t>
         </is>
       </c>
       <c r="F299" s="20" t="inlineStr">
@@ -42423,22 +42423,22 @@
       </c>
       <c r="E300" s="20" t="inlineStr">
         <is>
-          <t>12.32 (declared)</t>
+          <t>14.76 (Т2 26.08.2026 (неофиц. | unofficial))</t>
         </is>
       </c>
       <c r="F300" s="20" t="inlineStr">
         <is>
-          <t>11.00 – 13.00 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="AE300" s="19" t="inlineStr">
         <is>
-          <t>III · CC_THC12 : CBD1</t>
+          <t>II · CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="AF300" s="20" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-III</t>
+          <t>QCSP_001_CC-II</t>
         </is>
       </c>
     </row>
@@ -42458,7 +42458,7 @@
       </c>
       <c r="E301" s="20" t="inlineStr">
         <is>
-          <t>9.83 (declared)</t>
+          <t>9.55 (Т2 26.08.2026 (неофиц. | unofficial))</t>
         </is>
       </c>
       <c r="F301" s="20" t="inlineStr">
@@ -42528,22 +42528,22 @@
       </c>
       <c r="E303" s="20" t="inlineStr">
         <is>
-          <t>16.71 (declared)</t>
+          <t>21.01 (Т2 26.08.2026 (неофиц. | unofficial))</t>
         </is>
       </c>
       <c r="F303" s="20" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="AE303" s="19" t="inlineStr">
         <is>
-          <t>II · JD_THC16 : CBD1</t>
+          <t>I · JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AF303" s="20" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-II</t>
+          <t>QCSP_001_JD-I</t>
         </is>
       </c>
     </row>
@@ -42563,17 +42563,17 @@
       </c>
       <c r="E304" s="20" t="inlineStr">
         <is>
-          <t>15.63 (declared)</t>
+          <t>13.95 (Т2 26.08.2026 (неофиц. | unofficial))</t>
         </is>
       </c>
       <c r="F304" s="20" t="inlineStr">
         <is>
-          <t>14.40 – 17.60 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="AE304" s="19" t="inlineStr">
         <is>
-          <t>I · PUM_THC16 : CBD1</t>
+          <t>I · PUM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="AF304" s="20" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -43080,7 +43080,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>ACC102501 12.91 (декл.)</t>
+          <t>ACC102501 12.09 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -43289,12 +43289,12 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>BSS052501 20.39</t>
+          <t>BSS052501 20.52 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t>BSS1024 21.03 (26.02.2025)</t>
+          <t>BSS1024 21.03 (26.02.2025); BSS052501 20.39 (28.11.2025)</t>
         </is>
       </c>
     </row>
@@ -43326,22 +43326,22 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>CJ_THC24 : CBD1</t>
+          <t>CJ_THC28 : CBD1</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>27.00 – 29.00 %</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±1.99%</t>
+          <t>28.00% ±1.00%</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>CJ082501/1 24.96, CJ052501/01 24.05, CJ072501 23.70, CJ1024 23.00, CJ092501 22.30</t>
+          <t>CJ082501/1 28.34 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -43362,139 +43362,123 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC26 : CBD1</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>18.00 – 22.00 %</t>
+          <t>25.01 – 26.99 %</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±2.00%</t>
+          <t>26.00% ±0.99%</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>CJ062501/1 21.51, CJ062501/2 18.91, CJ082501/2 18.29</t>
+          <t>CJ092501 25.65 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t>CJ052501/01 20.29 (17.09.2025); CJ082501/2 20.84 (21.01.2026)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>17.61 – 17.99 %</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="inlineStr"/>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="inlineStr"/>
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>CJ_THC24 : CBD1</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>23.00 – 25.00 %</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>24.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>CJ062501/1 24.80 (Т2 неофиц.), CJ052501/01 24.05, CJ072501 23.70, CJ1024 23.00</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>CJ082501/1 24.96 (21.01.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>CJ_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>14.40 – 17.60 %</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±1.60%</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>CJ052501/02 14.93</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>CJ062501/2 16.56 (23.10.2025)</t>
-        </is>
-      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>22.01 – 22.99 %</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr"/>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cash Cow  (CC · 3 batches)</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC</t>
-        </is>
-      </c>
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>CC_THC18 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>CC012601/1 17.67</t>
+          <t>CJ062501/2 18.91, CJ082501/2 18.29</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CJ052501/01 20.29 (17.09.2025); CJ062501/1 21.51 (23.10.2025); CJ082501/2 20.84 (21.01.2026)</t>
         </is>
       </c>
     </row>
@@ -43511,7 +43495,7 @@
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>15.00 – 16.19 %</t>
+          <t>17.61 – 17.99 %</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr"/>
@@ -43529,90 +43513,71 @@
       <c r="D17" s="9" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>CC_THC14 : CBD1</t>
+          <t>CJ_THC16 : CBD1</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>13.01 – 14.99 %</t>
+          <t>14.40 – 17.60 %</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±0.99%</t>
+          <t>16.00% ±1.60%</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>CC112501 13.35</t>
+          <t>CJ052501/02 14.93</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CJ062501/2 16.56 (23.10.2025)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="13" t="inlineStr"/>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>CC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>11.00 – 13.00 %</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>12.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>CC012603 12.32 (декл.)</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>CJ092501 22.30 (21.01.2026) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Chem Flyer  (CF · 1 batches)</t>
+          <t>Cash Cow  (CC · 3 batches)</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>QCSP_001_CF</t>
+          <t>QCSP_001_CC</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -43622,22 +43587,22 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>CF_THC10 : CBD1</t>
+          <t>CC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>9.00 – 11.00 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>10.00% ±1.00%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>CF102501 9.83 (декл.)</t>
+          <t>CC012601/1 17.67</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -43647,101 +43612,57 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Clemosa a bud  (CLE · 1 batches)</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_CLE</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>CLE_THC8 : CBD1</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>7.20 – 8.80 %</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>8.00% ±0.80%</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>CLE072501 8.02</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>15.41 – 16.19 %</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="inlineStr"/>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Fat Bastard  (FB · 6 batches)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_FB</t>
-        </is>
-      </c>
+      <c r="A21" s="10" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="13" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>FB_THC22 : CBD1</t>
+          <t>CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.19%</t>
+          <t>14.00% ±1.40%</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>FB012603 20.83</t>
+          <t>CC012603 14.76 (Т2 неофиц.), CC112501 13.35</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -43751,33 +43672,49 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Chem Flyer  (CF · 1 batches)</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_CF</t>
+        </is>
+      </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>CF_THC10 : CBD1</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>9.00 – 11.00 %</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>10.00% ±1.00%</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
+          <t>CF102501 9.55 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -43787,57 +43724,101 @@
       </c>
     </row>
     <row r="23">
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>15.00 – 16.19 %</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="inlineStr"/>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="inlineStr"/>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Clemosa a bud  (CLE · 1 batches)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_CLE</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>CLE_THC8 : CBD1</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>7.20 – 8.80 %</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80%</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>CLE072501 8.65 (Т2 неофиц.)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>CLE072501 8.02 (21.01.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Fat Bastard  (FB · 6 batches)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB</t>
+        </is>
+      </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>13.01 – 14.99 %</t>
+          <t>18.86 – 21.14 %</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±0.99%</t>
+          <t>20.00% ±1.14%</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>FB012601/1 14.68</t>
+          <t>FB012603 20.83, FB012602 18.86</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -43853,27 +43834,27 @@
       <c r="D25" s="9" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>FB_THC12 : CBD1</t>
+          <t>FB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>11.00 – 13.00 %</t>
+          <t>17.15 – 18.85 %</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>12.00% ±1.00%</t>
+          <t>18.00% ±0.85%</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>FB032601 12.39</t>
+          <t>FB012603V 18.29, FB012601/1 17.99 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -43883,92 +43864,64 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Apr 2025</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Gorilla Glue  (GG · 7 batches)</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_GG</t>
-        </is>
-      </c>
+      <c r="A26" s="10" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="13" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>GG_THC18 : CBD1</t>
+          <t>FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>14.86 – 17.14 %</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.00%</t>
+          <t>16.00% ±1.14%</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
+          <t>FB112501 16.69</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
         <is>
-          <t>GG1024_01 17.22 (17.04.2025); GG012603 17.59 (30.06.2026)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr"/>
-      <c r="C27" s="13" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>GG_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>15.01 – 16.99 %</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>13.21 – 14.85 %</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr"/>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr"/>
@@ -43977,27 +43930,27 @@
       <c r="D28" s="9" t="inlineStr"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>FB_THC12 : CBD1</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>10.80 – 13.20 %</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±1.00%</t>
+          <t>12.00% ±1.20%</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>GG1024 13.34</t>
+          <t>FB032601 12.39</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -44007,80 +43960,73 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Apr 2025</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Grape Pie  (GP · 13 batches)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_GP</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>GP_THC24 : CBD1</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>21.60 – 26.40 %</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±2.40%</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>GP0824_02 23.19 (10.07.2025); GP0824_02 23.79 (22.05.2025)</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>FB012601/1 14.68 (11.05.2026) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>21.37 – 21.59 %</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr"/>
-      <c r="I30" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J30" s="25" t="inlineStr"/>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Gorilla Glue  (GG · 7 batches)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_GG</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>GG_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>17.01 – 18.99 %</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>18.00% ±0.99%</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>GG1024_01 17.22 (17.04.2025); GG012603 17.59 (30.06.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr"/>
@@ -44094,338 +44040,310 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±1.36%</t>
+          <t>16.00% ±1.00%</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
+          <t>GG012603 16.70, GG1024_02 15.95, GG1024 15.51 (Т2 неофиц.), GG012601* 15.35</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t>GP052501 18.98 (19.09.2025)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr"/>
-      <c r="C32" s="13" t="inlineStr"/>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>GP_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>17.37 – 18.63 %</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±0.63%</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>GP052501 18.52</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>GG1024 13.34 (23.04.2025) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr"/>
-      <c r="B33" s="9" t="inlineStr"/>
-      <c r="C33" s="13" t="inlineStr"/>
-      <c r="D33" s="9" t="inlineStr"/>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Grape Pie  (GP · 13 batches)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_GP</t>
+        </is>
+      </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>GP_THC16 : CBD1</t>
+          <t>GP_THC28 : CBD1</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>14.64 – 17.36 %</t>
+          <t>26.61 – 29.39 %</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±1.36%</t>
+          <t>28.00% ±1.39%</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>GP082501/2 15.70</t>
+          <t>GP0824_03 28.03 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>GP082501/2 14.83 (21.01.2026)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme  (GRC · 2 batches)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_GRC</t>
-        </is>
-      </c>
+      <c r="A34" s="10" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="13" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>GRC_THC12 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>10.80 – 13.20 %</t>
+          <t>25.40 – 26.60 %</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>12.00% ±1.20%</t>
+          <t>26.00% ±0.60%</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>GRC102501/2 11.53</t>
+          <t>P160012 26.32, P160022 25.72</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GP0824_03 25.45 (10.07.2025); GP092501 25.73 (21.01.2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>7.71 – 10.79 %</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="inlineStr"/>
-      <c r="I35" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J35" s="25" t="inlineStr"/>
+      <c r="A35" s="10" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr"/>
+      <c r="C35" s="13" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>GP_THC24 : CBD1</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>22.61 – 25.39 %</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>24.00% ±1.39%</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>GP092501 25.24 (Т2 неофиц.), GP082501/1 25.13 (Т2 неофиц.), GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>GP0824_02 23.19 (10.07.2025); GP0824_02 23.79 (22.05.2025)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr"/>
-      <c r="B36" s="9" t="inlineStr"/>
-      <c r="C36" s="13" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>GRC_THC7 : CBD1</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>6.30 – 7.70 %</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>7.00% ±0.70%</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>GRC102501/1 7.05 (декл.)</t>
-        </is>
-      </c>
-      <c r="J36" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>22.01 – 22.60 %</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr"/>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Jan 2025</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia  (HPA · 3 batches)</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_HPA</t>
-        </is>
-      </c>
+      <c r="A37" s="10" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr"/>
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.19%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>HPA1024_01 21.61, HPA052501 20.39</t>
+          <t>GP072501/1 21.36, GP0824_01 20.79, GP052501 18.52, GP072501/2 18.29 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">
         <is>
-          <t>HPA1024_01 22.43 (24.06.2025)</t>
+          <t>GP052501 18.98 (19.09.2025); GP072501/2 19.81 (21.01.2026); GP082501/1 21.29 (21.01.2026)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr"/>
-      <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>HPA_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>16.20 – 19.80 %</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80%</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>HPA1024 17.31</t>
-        </is>
-      </c>
-      <c r="J38" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>17.61 – 17.99 %</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr"/>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>ⓘ</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>superseded, outside spec</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>HPA1024 14.97 (23.01.2025) — pre-retest values, replaced per the retest rule (R5)</t>
+      <c r="A39" s="10" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr"/>
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>GP_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>14.40 – 17.60 %</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>16.00% ±1.60%</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>GP082501/2 15.70</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>GP082501/2 14.83 (21.01.2026)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donutz  (JD · 7 batches)</t>
+          <t>Graps &amp; Creme  (GRC · 2 batches)</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>QCSP_001_JD</t>
+          <t>QCSP_001_GRC</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -44435,27 +44353,27 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>GRC_THC10 : CBD1</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>18.00 – 22.00 %</t>
+          <t>9.00 – 11.00 %</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±2.00%</t>
+          <t>10.00% ±1.00%</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
+          <t>GRC102501/2 9.80 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J40" s="21" t="inlineStr">
         <is>
-          <t>JD112501 19.64 (11.05.2026)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -44472,7 +44390,7 @@
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>17.00 – 17.99 %</t>
+          <t>7.71 – 8.99 %</t>
         </is>
       </c>
       <c r="H41" s="25" t="inlineStr"/>
@@ -44495,22 +44413,22 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>JD_THC16 : CBD1</t>
+          <t>GRC_THC7 : CBD1</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>6.30 – 7.70 %</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>7.00% ±0.70%</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>JD012603/01 16.71 (декл.), JD012603/02V 15.16</t>
+          <t>GRC102501/1 7.05 (декл.)</t>
         </is>
       </c>
       <c r="J42" s="21" t="inlineStr">
@@ -44520,60 +44438,41 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr"/>
-      <c r="B43" s="9" t="inlineStr"/>
-      <c r="C43" s="13" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>JD_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>13.00 – 15.00 %</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>14.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>JD112501* 13.93</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>GRC102501/2 11.53 (04.03.2026) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jan 2025</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Jokerz 31  (J31 · 3 batches)</t>
+          <t>High Pro Amnesia  (HPA · 3 batches)</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>QCSP_001_J31</t>
+          <t>QCSP_001_HPA</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -44583,27 +44482,27 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>J31_THC22 : CBD1</t>
+          <t>HPA_THC22 : CBD1</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>21.00 – 23.00 %</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.19%</t>
+          <t>22.00% ±1.00%</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>J31122501 21.84, J31112501 20.21</t>
+          <t>HPA1024_01 21.61</t>
         </is>
       </c>
       <c r="J44" s="21" t="inlineStr">
         <is>
-          <t>J31122501 19.84 (09.04.2026)</t>
+          <t>HPA1024_01 22.43 (24.06.2025)</t>
         </is>
       </c>
     </row>
@@ -44619,118 +44518,102 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>HPA_THC20 : CBD1</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>19.01 – 20.99 %</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>20.00% ±0.99%</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>J31102501 17.32</t>
+          <t>HPA052501 19.69 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>J31102501 19.14 (04.03.2026)</t>
+          <t>HPA052501 20.39 (19.09.2025)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>ⓘ</t>
-        </is>
-      </c>
-      <c r="F46" s="22" t="inlineStr">
-        <is>
-          <t>superseded, outside spec</t>
-        </is>
-      </c>
-      <c r="I46" s="21" t="inlineStr">
-        <is>
-          <t>J31112501 25.27 (04.03.2026) — pre-retest values, replaced per the retest rule (R5)</t>
+      <c r="A46" s="10" t="inlineStr"/>
+      <c r="B46" s="9" t="inlineStr"/>
+      <c r="C46" s="13" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>HPA_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>17.00 – 19.00 %</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>18.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>HPA1024 17.31</t>
+        </is>
+      </c>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Kush Crasher  (KC · 1 batches)</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_KC</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>KC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>16.20 – 19.80 %</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80%</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>KC102501 17.04</t>
-        </is>
-      </c>
-      <c r="J47" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>HPA1024 14.97 (23.01.2025) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>May 2025</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Motor Breath  (MB · 2 batches)</t>
+          <t>Jelly Donutz  (JD · 7 batches)</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>QCSP_001_MB</t>
+          <t>QCSP_001_JD</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -44740,175 +44623,175 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>17.01 – 18.99 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±0.99%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>MB0824_04 18.67</t>
+          <t>JD012603/01 21.01 (Т2 неофиц.), JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
         </is>
       </c>
       <c r="J48" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JD112501 19.64 (11.05.2026); JD012603/02 20.54 (30.06.2026)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr"/>
-      <c r="B49" s="9" t="inlineStr"/>
-      <c r="C49" s="13" t="inlineStr"/>
-      <c r="D49" s="9" t="inlineStr"/>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>MB_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>15.00 – 17.00 %</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>MB0824_05 16.82</t>
-        </is>
-      </c>
-      <c r="J49" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>17.10 – 17.99 %</t>
+        </is>
+      </c>
+      <c r="H49" s="25" t="inlineStr"/>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Apr 2025</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa  (OPM · 8 batches)</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM</t>
-        </is>
-      </c>
+      <c r="A50" s="10" t="inlineStr"/>
+      <c r="B50" s="9" t="inlineStr"/>
+      <c r="C50" s="13" t="inlineStr"/>
+      <c r="D50" s="9" t="inlineStr"/>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC22 : CBD1</t>
+          <t>JD_THC16 : CBD1</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>19.80 – 24.20 %</t>
+          <t>14.91 – 17.09 %</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.20%</t>
+          <t>16.00% ±1.09%</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>OPM1024 20.03</t>
+          <t>JD012603/02V 17.09 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J50" s="21" t="inlineStr">
         <is>
-          <t>OPM1024 19.96 (23.04.2025)</t>
+          <t>JD012603/02V 15.16 (30.06.2026)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>19.01 – 19.79 %</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="inlineStr"/>
-      <c r="I51" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="inlineStr"/>
+      <c r="A51" s="10" t="inlineStr"/>
+      <c r="B51" s="9" t="inlineStr"/>
+      <c r="C51" s="13" t="inlineStr"/>
+      <c r="D51" s="9" t="inlineStr"/>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>JD_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>13.10 – 14.90 %</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>14.00% ±0.90%</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>JD012603/02 14.43 (Т2 неофиц.), JD112501* 13.93</t>
+        </is>
+      </c>
+      <c r="J51" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr"/>
-      <c r="B52" s="9" t="inlineStr"/>
-      <c r="C52" s="13" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr"/>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Jokerz 31  (J31 · 3 batches)</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_J31</t>
+        </is>
+      </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC18 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>19.81 – 24.19 %</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.00%</t>
+          <t>22.00% ±2.19%</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>OPM1024_02 18.04</t>
+          <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
       <c r="J52" s="21" t="inlineStr">
         <is>
-          <t>OPM1024_02 18.27 (24.06.2025)</t>
+          <t>J31122501 19.84 (09.04.2026)</t>
         </is>
       </c>
     </row>
@@ -44919,154 +44802,207 @@
       <c r="D53" s="9" t="inlineStr"/>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>J31102501 17.32</t>
         </is>
       </c>
       <c r="J53" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>J31102501 19.14 (04.03.2026)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr"/>
-      <c r="B54" s="9" t="inlineStr"/>
-      <c r="C54" s="13" t="inlineStr"/>
-      <c r="D54" s="9" t="inlineStr"/>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>OPM_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>13.00 – 15.00 %</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>14.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>OPM052501 14.16</t>
-        </is>
-      </c>
-      <c r="J54" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
+          <t>J31112501 25.27 (04.03.2026) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="E55" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>11.01 – 12.99 %</t>
-        </is>
-      </c>
-      <c r="H55" s="25" t="inlineStr"/>
-      <c r="I55" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J55" s="25" t="inlineStr"/>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Kush Crasher  (KC · 1 batches)</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_KC</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>KC_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>16.20 – 19.80 %</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80%</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>KC102501 17.06 (Т2 неофиц.)</t>
+        </is>
+      </c>
+      <c r="J55" s="21" t="inlineStr">
+        <is>
+          <t>KC102501 17.04 (04.03.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr"/>
-      <c r="B56" s="9" t="inlineStr"/>
-      <c r="C56" s="13" t="inlineStr"/>
-      <c r="D56" s="9" t="inlineStr"/>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Motor Breath  (MB · 2 batches)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_MB</t>
+        </is>
+      </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>9.00 – 11.00 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>10.00% ±1.00%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>OPM092501 9.43</t>
+          <t>MB0824_04 18.67, MB0824_05 17.93 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J56" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MB0824_05 16.82 (28.07.2025)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>documented gap</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>8.81 – 8.99 %</t>
-        </is>
-      </c>
-      <c r="H57" s="25" t="inlineStr"/>
-      <c r="I57" s="26" t="inlineStr">
-        <is>
-          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
-        </is>
-      </c>
-      <c r="J57" s="25" t="inlineStr"/>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa  (OPM · 8 batches)</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>OPM_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>19.81 – 24.19 %</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>22.00% ±2.19%</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>OPM1024 20.03</t>
+        </is>
+      </c>
+      <c r="J57" s="21" t="inlineStr">
+        <is>
+          <t>OPM1024 19.96 (23.04.2025)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr"/>
@@ -45075,86 +45011,58 @@
       <c r="D58" s="9" t="inlineStr"/>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>II</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC8 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>7.20 – 8.80 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>8.00% ±0.80%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>OPM112501 8.00, OPM122501 7.91</t>
+          <t>OPM1024_03 19.30 (Т2 неофиц.), OMP1024_01 18.99 (Т2 неофиц.), OPM1024_02 18.04</t>
         </is>
       </c>
       <c r="J58" s="21" t="inlineStr">
         <is>
-          <t>OPM122501 8.09 (09.04.2026)</t>
+          <t>OPM1024_02 18.27 (24.06.2025); OPM1024_03 16.55 (28.07.2025)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>Permanent Marker  (PM · 3 batches)</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_PM</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>PM_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>13.00 – 15.00 %</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>14.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>PM112501 13.33</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
-        <is>
-          <t>PM092501 14.06 (21.01.2026)</t>
-        </is>
-      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>15.41 – 16.19 %</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr"/>
+      <c r="I59" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J59" s="25" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr"/>
@@ -45163,174 +45071,118 @@
       <c r="D60" s="9" t="inlineStr"/>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>11.01 – 12.99 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>12.00% ±0.99%</t>
+          <t>14.00% ±1.40%</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>PM092501 12.25</t>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
       <c r="J60" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OMP1024_01 15.38 (06.05.2025)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr"/>
-      <c r="B61" s="9" t="inlineStr"/>
-      <c r="C61" s="13" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>PM_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>9.00 – 11.00 %</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>10.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>PM072501 10.01</t>
-        </is>
-      </c>
-      <c r="J61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>11.01 – 12.59 %</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr"/>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J61" s="25" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
-        <is>
-          <t>Pure Michigen  (PUM · 1 batches)</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_PUM</t>
-        </is>
-      </c>
+      <c r="A62" s="10" t="inlineStr"/>
+      <c r="B62" s="9" t="inlineStr"/>
+      <c r="C62" s="13" t="inlineStr"/>
+      <c r="D62" s="9" t="inlineStr"/>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>14.40 – 17.60 %</t>
+          <t>9.00 – 11.00 %</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±1.60%</t>
+          <t>10.00% ±1.00%</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>PUM102501 15.63 (декл.)</t>
+          <t>OPM092501 10.18 (Т2 неофиц.)</t>
         </is>
       </c>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OPM092501 9.43 (21.01.2026)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>Scrambler  (SCR · 4 batches)</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>SCR_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>19.81 – 24.19 %</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19%</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>SCR022601 21.92</t>
-        </is>
-      </c>
-      <c r="J63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>documented gap</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>8.81 – 8.99 %</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr"/>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>нема резултат | no result on file — a future result here triggers a grade-set revision</t>
+        </is>
+      </c>
+      <c r="J63" s="25" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr"/>
@@ -45339,54 +45191,54 @@
       <c r="D64" s="9" t="inlineStr"/>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>SCR_THC18 : CBD1</t>
+          <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>7.20 – 8.80 %</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>8.00% ±0.80%</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>SCR012601 18.07 (декл.), SCR012603 17.84, SCR112501 17.13</t>
+          <t>OPM112501 8.00, OPM122501 7.91</t>
         </is>
       </c>
       <c r="J64" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OPM122501 8.09 (09.04.2026)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>Sleepy Joy  (SJ · 3 batches)</t>
+          <t>Permanent Marker  (PM · 3 batches)</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>QCSP_001_SJ</t>
+          <t>QCSP_001_PM</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -45396,7 +45248,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>SJ_THC12 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -45411,7 +45263,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>SJ102501 11.20</t>
+          <t>PM092501 12.25</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr">
@@ -45432,7 +45284,7 @@
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>SJ_THC10 : CBD1</t>
+          <t>PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -45447,7 +45299,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>SJ092501 10.96, SJ112501 9.20</t>
+          <t>PM112501 10.79 (Т2 неофиц.), PM072501 10.01</t>
         </is>
       </c>
       <c r="J66" s="21" t="inlineStr">
@@ -45457,106 +45309,351 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>Wedding Cake  (WED · 1 batches)</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>QCSP_001_WED</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>WED_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>19.80 – 24.20 %</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20%</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>WED102501 22.05 (декл.)</t>
-        </is>
-      </c>
-      <c r="J67" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>ⓘ</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>superseded, outside spec</t>
+        </is>
+      </c>
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>PM092501 14.06 (21.01.2026); PM112501 13.33 (05.03.2026) — pre-retest values, replaced per the retest rule (R5)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Pure Michigen  (PUM · 1 batches)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_PUM</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>PUM_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>12.60 – 15.40 %</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>14.00% ±1.40%</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>PUM102501 13.95 (Т2 неофиц.)</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Scrambler  (SCR · 4 batches)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_SCR</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>SCR_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>19.81 – 24.19 %</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>22.00% ±2.19%</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>SCR022601 21.92</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr"/>
+      <c r="B70" s="9" t="inlineStr"/>
+      <c r="C70" s="13" t="inlineStr"/>
+      <c r="D70" s="9" t="inlineStr"/>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>SCR_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>16.20 – 19.80 %</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80%</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>SCR112501 19.73 (Т2 неофиц.), SCR012601 18.07 (декл.), SCR012603 17.84</t>
+        </is>
+      </c>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
+          <t>SCR112501 17.13 (11.05.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Sleepy Joy  (SJ · 3 batches)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>SJ_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>11.01 – 12.99 %</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>12.00% ±0.99%</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>SJ102501 11.20</t>
+        </is>
+      </c>
+      <c r="J71" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr"/>
+      <c r="B72" s="9" t="inlineStr"/>
+      <c r="C72" s="13" t="inlineStr"/>
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>SJ_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>9.00 – 11.00 %</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>SJ092501 10.39 (Т2 неофиц.), SJ112501 9.20</t>
+        </is>
+      </c>
+      <c r="J72" s="21" t="inlineStr">
+        <is>
+          <t>SJ092501 10.96 (21.01.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Wedding Cake  (WED · 1 batches)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>QCSP_001_WED</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>WED_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>19.80 – 24.20 %</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20%</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>WED102501 22.05 (декл.)</t>
+        </is>
+      </c>
+      <c r="J73" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>Wedding Crasher  (WC · 2 batches)</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>QCSP_001_WC</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>19.80 – 24.20 %</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="H74" s="9" t="inlineStr">
         <is>
           <t>22.00% ±2.20%</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>WC072501 22.11, WC082501 21.67</t>
-        </is>
-      </c>
-      <c r="J68" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>WC082501 23.48 (Т2 неофиц.), WC072501 22.11</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>WC082501 21.67 (21.01.2026)</t>
         </is>
       </c>
     </row>
@@ -45599,7 +45696,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>86 batches · anchor = latest (retest = CoQ-forming) certified Total Δ⁹-THC; declared where no eCoA yet · mandatory management codes: 46/48 exact, 2 flagged unavoidable deviations</t>
+          <t>86 batches · anchor = CoQ-forming Total Δ⁹-THC (T1+T2 re-analysis of 26.08.2026 where retested; T2 values unofficial pending formal eCoAs; declared where no analysis) · mandatory management codes revised 27.08.2026: 42/48 exact, 6 flagged unavoidable deviations</t>
         </is>
       </c>
     </row>
@@ -45691,17 +45788,17 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>declared</t>
+          <t>T2 re-analysis</t>
         </is>
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -45731,7 +45828,7 @@
       </c>
       <c r="M5" s="28" t="inlineStr">
         <is>
-          <t>declared — no eCoA yet, grade provisional</t>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
@@ -45968,248 +46065,264 @@
       <c r="M9" s="21" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>P050192</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr">
-        <is>
-          <t>In-house GC cross-check NGP/QCG/SOP-024,</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>20.52</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_BSS</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>BSS_THC20 : CBD1</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>18.00 – 22.00 %</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>20.00% ±2.00%</t>
         </is>
       </c>
-      <c r="M10" s="21" t="inlineStr"/>
+      <c r="M10" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>P060022</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t>ППК26002, 21.01.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>28.34</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_CJ</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>CJ_THC24 : CBD1</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>22.01 – 25.99 %</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±1.99%</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>CJ_THC28 : CBD1</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>27.00 – 29.00 %</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>28.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M11" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>CJ052501/01</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>P050162</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>P060072</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t>197-3-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_CJ</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>CJ_THC24 : CBD1</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>22.01 – 25.99 %</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±1.99%</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>CJ_THC26 : CBD1</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>25.01 – 26.99 %</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>26.00% ±0.99%</t>
+        </is>
+      </c>
+      <c r="M12" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>CJ072501</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>P050252</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>CJ062501/1</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>P050222</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>23.70</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="inlineStr">
-        <is>
-          <t>ППК25367, 28.11.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>24.80</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_CJ</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>22.01 – 25.99 %</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±1.99%</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>23.00 – 25.00 %</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>24.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M13" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -46217,10 +46330,14 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>CJ1024</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
+          <t>CJ052501/01</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>P050162</t>
+        </is>
+      </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Cap Junky</t>
@@ -46228,7 +46345,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -46238,7 +46355,7 @@
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>ППК25052, 26.02.2025, UKIM</t>
+          <t>197-3-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -46248,7 +46365,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -46258,12 +46375,12 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±1.99%</t>
+          <t>24.00% ±1.00%</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr"/>
@@ -46274,12 +46391,12 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>P060072</t>
+          <t>P050252</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -46289,7 +46406,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -46299,7 +46416,7 @@
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>ППК26007, 21.01.2026, UKIM</t>
+          <t>ППК25367, 28.11.2025, UKIM</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -46309,7 +46426,7 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -46319,80 +46436,72 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>22.01 – 25.99 %</t>
+          <t>23.00 – 25.00 %</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±1.99%</t>
+          <t>24.00% ±1.00%</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>CJ062501/1</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>P050222</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>CJ1024</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>certificate</t>
         </is>
       </c>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>ППК25321, 23.10.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>ППК25052, 26.02.2025, UKIM</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>QCSP_001_CJ</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>CJ_THC20 : CBD1</t>
-        </is>
-      </c>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>18.00 – 22.00 %</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>20.00% ±2.00%</t>
-        </is>
-      </c>
-      <c r="M16" s="34" t="inlineStr">
-        <is>
-          <t>MANDATORY-CODE DEVIATION: THC22 impossible beside THC24 holding 22.30 — regraded THC20</t>
-        </is>
-      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>CJ_THC24 : CBD1</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>23.00 – 25.00 %</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>24.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -46435,7 +46544,7 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -46496,7 +46605,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -46557,7 +46666,7 @@
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -46639,130 +46748,130 @@
       <c r="M20" s="21" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>CC112501</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>P060272</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>CC012603</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>P060372</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G21" s="29" t="inlineStr">
-        <is>
-          <t>ППК26068, 11.05.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_CC</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>CC_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>13.01 – 14.99 %</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>14.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr"/>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>12.60 – 15.40 %</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>14.00% ±1.40%</t>
+        </is>
+      </c>
+      <c r="M21" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>CC012603</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>P060372</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>CC112501</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>P060272</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>declared</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="inlineStr">
-        <is>
-          <t>owner-declared value</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>certificate</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>ППК26068, 11.05.2026, UKIM</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>QCSP_001_CC</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>CC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>11.00 – 13.00 %</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>12.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="M22" s="28" t="inlineStr">
-        <is>
-          <t>declared — no eCoA yet, grade provisional</t>
-        </is>
-      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>CC_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>12.60 – 15.40 %</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>14.00% ±1.40%</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -46785,17 +46894,17 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>declared</t>
+          <t>T2 re-analysis</t>
         </is>
       </c>
       <c r="G23" s="27" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -46825,70 +46934,74 @@
       </c>
       <c r="M23" s="28" t="inlineStr">
         <is>
-          <t>declared — no eCoA yet, grade provisional</t>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>P050282</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>8.02</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G24" s="29" t="inlineStr">
-        <is>
-          <t>PP CoA #027 / ППК25370, 21.01.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>8.65</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_CLE</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>CLE_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>7.20 – 8.80 %</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>8.00% ±0.80%</t>
         </is>
       </c>
-      <c r="M24" s="21" t="inlineStr"/>
+      <c r="M24" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -46932,17 +47045,17 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>FB_THC22 : CBD1</t>
+          <t>FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>18.86 – 21.14 %</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.19%</t>
+          <t>20.00% ±1.14%</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr"/>
@@ -46988,22 +47101,22 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>18.86 – 21.14 %</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>20.00% ±1.14%</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr"/>
@@ -47059,76 +47172,80 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>17.15 – 18.85 %</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>18.00% ±0.85%</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>FB112501</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>P060292</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>FB012601/1</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G28" s="29" t="inlineStr">
-        <is>
-          <t>ППК26066, 11.05.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>17.99</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_FB</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="32" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>16.20 – 19.80 %</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80%</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>17.15 – 18.85 %</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>18.00% ±0.85%</t>
+        </is>
+      </c>
+      <c r="M28" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION: owner code THC16 infeasible for 17.99 (max window 14.40-17.60) -&gt; THC18</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -47136,12 +47253,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -47151,7 +47268,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -47161,7 +47278,7 @@
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>ППК26067, 11.05.2026, UKIM</t>
+          <t>ППК26066, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -47176,17 +47293,17 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>13.01 – 14.99 %</t>
+          <t>14.86 – 17.14 %</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±0.99%</t>
+          <t>16.00% ±1.14%</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr"/>
@@ -47238,12 +47355,12 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>11.00 – 13.00 %</t>
+          <t>10.80 – 13.20 %</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>12.00% ±1.00%</t>
+          <t>12.00% ±1.20%</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr"/>
@@ -47295,12 +47412,12 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.00%</t>
+          <t>18.00% ±0.99%</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr"/>
@@ -47356,12 +47473,12 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.00%</t>
+          <t>18.00% ±0.99%</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr"/>
@@ -47417,12 +47534,12 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>17.00 – 19.00 %</t>
+          <t>17.01 – 18.99 %</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.00%</t>
+          <t>18.00% ±0.99%</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr"/>
@@ -47478,12 +47595,12 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>16.00% ±1.00%</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr"/>
@@ -47539,76 +47656,76 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>16.00% ±1.00%</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>GG012601*</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>P060302</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>GG1024</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr"/>
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G36" s="29" t="inlineStr">
-        <is>
-          <t>ППК26062, 11.05.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>15.51</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_GG</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>GG_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>15.01 – 16.99 %</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr"/>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>15.00 – 17.00 %</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>16.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M36" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -47616,10 +47733,14 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>GG1024</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr"/>
+          <t>GG012601*</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
@@ -47627,7 +47748,7 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -47637,7 +47758,7 @@
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>n/a — Purely Plant in-house CoA (Batch G</t>
+          <t>ППК26062, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -47647,86 +47768,90 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>15.00 – 17.00 %</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±1.00%</t>
+          <t>16.00% ±1.00%</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G38" s="29" t="inlineStr">
-        <is>
-          <t>ППК26117, 06.07.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>28.03</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_GP</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>GP_THC24 : CBD1</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>21.60 – 26.40 %</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±2.40%</t>
-        </is>
-      </c>
-      <c r="M38" s="21" t="inlineStr"/>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>GP_THC28 : CBD1</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>26.61 – 29.39 %</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>28.00% ±1.39%</t>
+        </is>
+      </c>
+      <c r="M38" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -47734,12 +47859,12 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>P060092</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -47749,7 +47874,7 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -47759,7 +47884,7 @@
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>ППК26009, 21.01.2026, UKIM</t>
+          <t>ППК26117, 06.07.2026, UKIM</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -47769,22 +47894,22 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>25.40 – 26.60 %</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±2.40%</t>
+          <t>26.00% ±0.60%</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr"/>
@@ -47830,147 +47955,155 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>25.40 – 26.60 %</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±2.40%</t>
+          <t>26.00% ±0.60%</t>
         </is>
       </c>
       <c r="M40" s="21" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>GP0824_03</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>P050072</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>P060092</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G41" s="29" t="inlineStr">
-        <is>
-          <t>ППК25175, 10.07.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
+        <is>
+          <t>25.24</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G41" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_GP</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>21.60 – 26.40 %</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±2.40%</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>22.61 – 25.39 %</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
+          <t>24.00% ±1.39%</t>
+        </is>
+      </c>
+      <c r="M41" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.24 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>P050202</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>GP082501/1</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>P050312</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G42" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In-house HPLC cross-check NPCCC/SCP-02, </t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>25.13</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G42" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_GP</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="I42" s="32" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>21.60 – 26.40 %</t>
-        </is>
-      </c>
-      <c r="L42" s="9" t="inlineStr">
-        <is>
-          <t>24.00% ±2.40%</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr"/>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>22.61 – 25.39 %</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr">
+        <is>
+          <t>24.00% ±1.39%</t>
+        </is>
+      </c>
+      <c r="M42" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.13 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -47978,12 +48111,12 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P050202</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -47993,7 +48126,7 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -48003,7 +48136,7 @@
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, UKIM</t>
+          <t xml:space="preserve">In-house HPLC cross-check NPCCC/SCP-02, </t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -48013,7 +48146,7 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -48023,12 +48156,12 @@
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±2.40%</t>
+          <t>24.00% ±1.39%</t>
         </is>
       </c>
       <c r="M43" s="21" t="inlineStr"/>
@@ -48039,12 +48172,12 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>P050022</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -48054,7 +48187,7 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -48064,7 +48197,7 @@
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>197-11-К/26, 07.08.2026, FARM</t>
+          <t>ППК26119, 06.07.2026, UKIM</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -48074,7 +48207,7 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -48084,12 +48217,12 @@
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>21.60 – 26.40 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>24.00% ±2.40%</t>
+          <t>24.00% ±1.39%</t>
         </is>
       </c>
       <c r="M44" s="21" t="inlineStr"/>
@@ -48100,12 +48233,12 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>GP072501/1</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>P050292</t>
+          <t>P050022</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -48115,7 +48248,7 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -48125,7 +48258,7 @@
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>PP CoA #018 / ППК25378, 21.01.2026, UKIM</t>
+          <t>197-11-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -48135,22 +48268,22 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>22.61 – 25.39 %</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±1.36%</t>
+          <t>24.00% ±1.39%</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr"/>
@@ -48161,12 +48294,12 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>GP082501/1</t>
+          <t>GP072501/1</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>P050312</t>
+          <t>P050292</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -48176,7 +48309,7 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -48186,7 +48319,7 @@
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>PP CoA #020 / ППК25380, 21.01.2026, UKIM</t>
+          <t>PP CoA #018 / ППК25378, 21.01.2026, UKIM</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -48196,7 +48329,7 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
@@ -48206,12 +48339,12 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±1.36%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="M46" s="21" t="inlineStr"/>
@@ -48257,7 +48390,7 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
@@ -48267,12 +48400,12 @@
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±1.36%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="M47" s="21" t="inlineStr"/>
@@ -48283,12 +48416,12 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>GP072501/2</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>P050302</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -48298,7 +48431,7 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -48308,7 +48441,7 @@
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>PP CoA #019 / ППК25379, 21.01.2026, UKIM</t>
+          <t>197-10-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -48318,7 +48451,7 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
@@ -48328,76 +48461,80 @@
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>18.64 – 21.36 %</t>
+          <t>18.00 – 22.00 %</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>20.00% ±1.36%</t>
+          <t>20.00% ±2.00%</t>
         </is>
       </c>
       <c r="M48" s="21" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>GP052501</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>P050152</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>GP072501/2</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>P050302</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G49" s="29" t="inlineStr">
-        <is>
-          <t>197-10-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>18.29</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G49" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_GP</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>GP_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="K49" s="9" t="inlineStr">
-        <is>
-          <t>17.37 – 18.63 %</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±0.63%</t>
-        </is>
-      </c>
-      <c r="M49" s="21" t="inlineStr"/>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>GP_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>18.00 – 22.00 %</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>20.00% ±2.00%</t>
+        </is>
+      </c>
+      <c r="M49" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n">
@@ -48440,7 +48577,7 @@
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
@@ -48450,76 +48587,80 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>14.64 – 17.36 %</t>
+          <t>14.40 – 17.60 %</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±1.36%</t>
+          <t>16.00% ±1.60%</t>
         </is>
       </c>
       <c r="M50" s="21" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="30" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>P060182</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="31" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>11.53</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G51" s="29" t="inlineStr">
-        <is>
-          <t>051-6-K/26, 04.03.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G51" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_GRC</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I51" s="32" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>GRC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="K51" s="9" t="inlineStr">
-        <is>
-          <t>10.80 – 13.20 %</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>12.00% ±1.20%</t>
-        </is>
-      </c>
-      <c r="M51" s="21" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>GRC_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>9.00 – 11.00 %</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M51" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION: owner code THC12 infeasible for 9.80 (max window 10.80-13.20) -&gt; THC10</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="20" t="n">
@@ -48633,76 +48774,80 @@
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>19.81 – 24.19 %</t>
+          <t>21.00 – 23.00 %</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.19%</t>
+          <t>22.00% ±1.00%</t>
         </is>
       </c>
       <c r="M53" s="21" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n">
+      <c r="A54" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G54" s="29" t="inlineStr">
-        <is>
-          <t>ППК25278, 19.09.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_HPA</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>HPA_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>19.81 – 24.19 %</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19%</t>
-        </is>
-      </c>
-      <c r="M54" s="21" t="inlineStr"/>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="J54" s="20" t="inlineStr">
+        <is>
+          <t>HPA_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t>19.01 – 20.99 %</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>20.00% ±0.99%</t>
+        </is>
+      </c>
+      <c r="M54" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -48741,7 +48886,7 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
@@ -48751,76 +48896,80 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>16.20 – 19.80 %</t>
+          <t>17.00 – 19.00 %</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±1.80%</t>
+          <t>18.00% ±1.00%</t>
         </is>
       </c>
       <c r="M55" s="21" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n">
+      <c r="A56" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>JD012603/02</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>P060412</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>JD012603/01</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G56" s="29" t="inlineStr">
-        <is>
-          <t>ППК26113, 30.06.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>21.01</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G56" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_JD</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
       </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>18.00 – 22.00 %</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr">
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>20.00% ±2.00%</t>
         </is>
       </c>
-      <c r="M56" s="21" t="inlineStr"/>
+      <c r="M56" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -49007,12 +49156,12 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>P060362</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -49022,17 +49171,17 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>declared</t>
+          <t>T2 re-analysis</t>
         </is>
       </c>
       <c r="G60" s="27" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
         </is>
       </c>
       <c r="H60" s="20" t="inlineStr">
@@ -49052,80 +49201,84 @@
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>14.91 – 17.09 %</t>
         </is>
       </c>
       <c r="L60" s="20" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>16.00% ±1.09%</t>
         </is>
       </c>
       <c r="M60" s="28" t="inlineStr">
         <is>
-          <t>declared — no eCoA yet, grade provisional</t>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="n">
+      <c r="A61" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>JD012603/02V</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>JD012603/02</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="D61" s="31" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G61" s="29" t="inlineStr">
-        <is>
-          <t>ППК26111, 30.06.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="E61" s="32" t="inlineStr">
+        <is>
+          <t>14.43</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G61" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_JD</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>JD_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>15.01 – 16.99 %</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="M61" s="21" t="inlineStr"/>
+      <c r="I61" s="32" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>JD_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>13.10 – 14.90 %</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>14.00% ±0.90%</t>
+        </is>
+      </c>
+      <c r="M61" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION: owner code THC20 infeasible for 14.43 (max window 18.00-22.00) -&gt; THC14</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -49174,12 +49327,12 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>13.10 – 14.90 %</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±1.00%</t>
+          <t>14.00% ±0.90%</t>
         </is>
       </c>
       <c r="M62" s="21" t="inlineStr"/>
@@ -49364,65 +49517,69 @@
       <c r="M65" s="21" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n">
+      <c r="A66" s="20" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>P060172</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Kush Crasher</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G66" s="29" t="inlineStr">
-        <is>
-          <t>051-4-K/26, 04.03.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G66" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_KC</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="I66" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr">
+      <c r="J66" s="20" t="inlineStr">
         <is>
           <t>KC_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K66" s="20" t="inlineStr">
         <is>
           <t>16.20 – 19.80 %</t>
         </is>
       </c>
-      <c r="L66" s="9" t="inlineStr">
+      <c r="L66" s="20" t="inlineStr">
         <is>
           <t>18.00% ±1.80%</t>
         </is>
       </c>
-      <c r="M66" s="21" t="inlineStr"/>
+      <c r="M66" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -49475,76 +49632,80 @@
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
-          <t>17.01 – 18.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>18.00% ±0.99%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="M67" s="21" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n">
+      <c r="A68" s="20" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>P050112</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G68" s="29" t="inlineStr">
-        <is>
-          <t>ППК52211, 28.07.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>17.93</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G68" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_MB</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>MB_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>15.00 – 17.00 %</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="M68" s="21" t="inlineStr"/>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>MB_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
+        <is>
+          <t>16.20 – 19.80 %</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80%</t>
+        </is>
+      </c>
+      <c r="M68" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
@@ -49593,137 +49754,145 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>19.80 – 24.20 %</t>
+          <t>19.81 – 24.19 %</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
-          <t>22.00% ±2.20%</t>
+          <t>22.00% ±2.19%</t>
         </is>
       </c>
       <c r="M69" s="21" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n">
+      <c r="A70" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>OPM1024_02</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>P050062</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>18.04</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>197-18-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>19.30</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G70" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_OPM</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr">
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>17.00 – 19.00 %</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>18.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="M70" s="21" t="inlineStr"/>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>16.20 – 19.80 %</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80%</t>
+        </is>
+      </c>
+      <c r="M70" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="20" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>OPM1024_03</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>P050082</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>OMP1024_01</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>P050042</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>ППК25210, 28.07.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G71" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_OPM</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>OPM_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>15.01 – 16.99 %</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>16.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="M71" s="21" t="inlineStr"/>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="J71" s="20" t="inlineStr">
+        <is>
+          <t>OPM_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>16.20 – 19.80 %</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80%</t>
+        </is>
+      </c>
+      <c r="M71" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -49731,12 +49900,12 @@
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>P050042</t>
+          <t>P050062</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -49746,7 +49915,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
@@ -49756,7 +49925,7 @@
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>ППК25117, 06.05.2025, UKIM</t>
+          <t>197-18-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -49766,22 +49935,22 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>15.01 – 16.99 %</t>
+          <t>16.20 – 19.80 %</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>16.00% ±0.99%</t>
+          <t>18.00% ±1.80%</t>
         </is>
       </c>
       <c r="M72" s="21" t="inlineStr"/>
@@ -49827,7 +49996,7 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
@@ -49837,76 +50006,80 @@
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>13.00 – 15.00 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>14.00% ±1.00%</t>
+          <t>14.00% ±1.40%</t>
         </is>
       </c>
       <c r="M73" s="21" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n">
+      <c r="A74" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>P060042</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>9.43</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G74" s="29" t="inlineStr">
-        <is>
-          <t>ППК26008, 21.01.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_OPM</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="J74" s="20" t="inlineStr">
         <is>
           <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="20" t="inlineStr">
         <is>
           <t>9.00 – 11.00 %</t>
         </is>
       </c>
-      <c r="L74" s="9" t="inlineStr">
+      <c r="L74" s="20" t="inlineStr">
         <is>
           <t>10.00% ±1.00%</t>
         </is>
       </c>
-      <c r="M74" s="21" t="inlineStr"/>
+      <c r="M74" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
@@ -49949,7 +50122,7 @@
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -50010,7 +50183,7 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
@@ -50031,130 +50204,130 @@
       <c r="M76" s="21" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="14" t="n">
+      <c r="A77" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>PM112501</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>P060232</t>
-        </is>
-      </c>
-      <c r="D77" s="31" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>P060062</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>13.33</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>12.25</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>certificate</t>
         </is>
       </c>
-      <c r="G77" s="33" t="inlineStr">
-        <is>
-          <t>ППК26030, 05.03.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>197-20-К/26, 07.08.2026, FARM</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t>QCSP_001_PM</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>PM_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="K77" s="14" t="inlineStr">
-        <is>
-          <t>13.00 – 15.00 %</t>
-        </is>
-      </c>
-      <c r="L77" s="14" t="inlineStr">
-        <is>
-          <t>14.00% ±1.00%</t>
-        </is>
-      </c>
-      <c r="M77" s="34" t="inlineStr">
-        <is>
-          <t>MANDATORY-CODE DEVIATION: audited 13.33 &gt; 13.20 ceiling of THC12 — regraded THC14</t>
-        </is>
-      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>PM_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>11.01 – 12.99 %</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>12.00% ±0.99%</t>
+        </is>
+      </c>
+      <c r="M77" s="21" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n">
+      <c r="A78" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>PM092501</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>P060062</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
+        <is>
+          <t>PM112501</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>P060232</t>
+        </is>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>197-20-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>10.79</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
         <is>
           <t>QCSP_001_PM</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="I78" s="32" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>PM_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="K78" s="9" t="inlineStr">
-        <is>
-          <t>11.01 – 12.99 %</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr">
-        <is>
-          <t>12.00% ±0.99%</t>
-        </is>
-      </c>
-      <c r="M78" s="21" t="inlineStr"/>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>PM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>9.00 – 11.00 %</t>
+        </is>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00%</t>
+        </is>
+      </c>
+      <c r="M78" s="34" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION: owner code THC12 infeasible for 10.79 (max window 10.80-13.20) -&gt; THC10</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
@@ -50197,7 +50370,7 @@
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
@@ -50238,17 +50411,17 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>declared</t>
+          <t>T2 re-analysis</t>
         </is>
       </c>
       <c r="G80" s="27" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
         </is>
       </c>
       <c r="H80" s="20" t="inlineStr">
@@ -50263,22 +50436,22 @@
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>PUM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="K80" s="20" t="inlineStr">
         <is>
-          <t>14.40 – 17.60 %</t>
+          <t>12.60 – 15.40 %</t>
         </is>
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>16.00% ±1.60%</t>
+          <t>14.00% ±1.40%</t>
         </is>
       </c>
       <c r="M80" s="28" t="inlineStr">
         <is>
-          <t>declared — no eCoA yet, grade provisional</t>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
@@ -50345,10 +50518,14 @@
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>SCR012601</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr"/>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
       <c r="D82" s="19" t="inlineStr">
         <is>
           <t>Scrambler</t>
@@ -50356,17 +50533,17 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>declared</t>
+          <t>T2 re-analysis</t>
         </is>
       </c>
       <c r="G82" s="27" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
         </is>
       </c>
       <c r="H82" s="20" t="inlineStr">
@@ -50396,70 +50573,70 @@
       </c>
       <c r="M82" s="28" t="inlineStr">
         <is>
-          <t>declared — no eCoA yet, grade provisional</t>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="n">
+      <c r="A83" s="20" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>SCR012603</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>SCR012601</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr"/>
+      <c r="D83" s="19" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G83" s="29" t="inlineStr">
-        <is>
-          <t>197-21-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>18.07</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>declared</t>
+        </is>
+      </c>
+      <c r="G83" s="27" t="inlineStr">
+        <is>
+          <t>owner-declared value</t>
+        </is>
+      </c>
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_SCR</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I83" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
+      <c r="J83" s="20" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="K83" s="20" t="inlineStr">
         <is>
           <t>16.20 – 19.80 %</t>
         </is>
       </c>
-      <c r="L83" s="9" t="inlineStr">
+      <c r="L83" s="20" t="inlineStr">
         <is>
           <t>18.00% ±1.80%</t>
         </is>
       </c>
-      <c r="M83" s="21" t="inlineStr"/>
+      <c r="M83" s="28" t="inlineStr">
+        <is>
+          <t>declared — no eCoA yet, grade provisional</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
@@ -50467,12 +50644,12 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -50482,7 +50659,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
@@ -50492,7 +50669,7 @@
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, UKIM</t>
+          <t>197-21-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -50584,65 +50761,69 @@
       <c r="M85" s="21" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n">
+      <c r="A86" s="20" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="B86" s="18" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>P060082</t>
         </is>
       </c>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="D86" s="19" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G86" s="29" t="inlineStr">
-        <is>
-          <t>ППК26006, 21.01.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>10.39</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G86" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_SJ</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
+      <c r="I86" s="17" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
+      <c r="J86" s="20" t="inlineStr">
         <is>
           <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="K86" s="9" t="inlineStr">
+      <c r="K86" s="20" t="inlineStr">
         <is>
           <t>9.00 – 11.00 %</t>
         </is>
       </c>
-      <c r="L86" s="9" t="inlineStr">
+      <c r="L86" s="20" t="inlineStr">
         <is>
           <t>10.00% ±1.00%</t>
         </is>
       </c>
-      <c r="M86" s="21" t="inlineStr"/>
+      <c r="M86" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
@@ -50767,65 +50948,69 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="n">
+      <c r="A89" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>WC072501</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>P050262</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>certificate</t>
-        </is>
-      </c>
-      <c r="G89" s="29" t="inlineStr">
-        <is>
-          <t>ППК25369, 28.11.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>23.48</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>T2 re-analysis</t>
+        </is>
+      </c>
+      <c r="G89" s="27" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unoffi</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
         <is>
           <t>QCSP_001_WC</t>
         </is>
       </c>
-      <c r="I89" s="10" t="inlineStr">
+      <c r="I89" s="17" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K89" s="20" t="inlineStr">
         <is>
           <t>19.80 – 24.20 %</t>
         </is>
       </c>
-      <c r="L89" s="9" t="inlineStr">
+      <c r="L89" s="20" t="inlineStr">
         <is>
           <t>22.00% ±2.20%</t>
         </is>
       </c>
-      <c r="M89" s="21" t="inlineStr"/>
+      <c r="M89" s="28" t="inlineStr">
+        <is>
+          <t>T2 re-analysis (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
@@ -50833,12 +51018,12 @@
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>P060012</t>
+          <t>P050262</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -50848,7 +51033,7 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
@@ -50858,7 +51043,7 @@
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>ППК26001, 21.01.2026, UKIM</t>
+          <t>ППК25369, 28.11.2025, UKIM</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
